--- a/reports/二级子公司C_利润表_2025-05.xlsx
+++ b/reports/二级子公司C_利润表_2025-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>91020208</v>
+        <v>92496992</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>88399772</v>
+        <v>87807366</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>410885390</v>
+        <v>409356120</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>410259</v>
+        <v>414212</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1912564</v>
+        <v>1918147</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>359741</v>
+        <v>361870</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1672525</v>
+        <v>1679779</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>309119</v>
+        <v>309482</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1433361</v>
+        <v>1440515</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>289209</v>
+        <v>288125</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1338185</v>
+        <v>1344562</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>155231</v>
+        <v>153990</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>717372</v>
+        <v>720027</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>124321</v>
+        <v>122974</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>574449</v>
+        <v>575588</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>89372328</v>
+        <v>90846339</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>86751892</v>
+        <v>86156713</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82654944</v>
+        <v>82022421</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>384030602</v>
+        <v>382575877</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1236882</v>
+        <v>1232798</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>5762471</v>
+        <v>5734876</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>822523</v>
+        <v>823882</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>3841292</v>
+        <v>3822280</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3077690</v>
+        <v>3097200</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>14397374</v>
+        <v>14336339</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>409745</v>
+        <v>413810</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1918011</v>
+        <v>1912672</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>307146</v>
+        <v>310756</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1437016</v>
+        <v>1435813</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>512183</v>
+        <v>518076</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>2392531</v>
+        <v>2395554</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>615541</v>
+        <v>621221</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2868564</v>
+        <v>2877585</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2570400</v>
+        <v>2584097</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>11946040</v>
+        <v>11999470</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>50036</v>
+        <v>50062</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>249377</v>
+        <v>250591</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1234413</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>5762260</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>821054</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3839834</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>61810470</v>
+        <v>65657213</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>55052812</v>
+        <v>54487158</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>53813351</v>
+        <v>53256544</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>249466424</v>
+        <v>248874808</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1239461</v>
+        <v>1230614</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>5760865</v>
+        <v>5738023</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2055299</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>9557565</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>659328</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3057825</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>413087</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1911624</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>496682</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2295452</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>372944</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1723211</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>248666</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1150028</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>207037</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>959312</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>925645</v>
+        <v>930017</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>4300405</v>
+        <v>4320160</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>721760</v>
+        <v>721650</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3344619</v>
+        <v>3361405</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>620091</v>
+        <v>617004</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2867960</v>
+        <v>2881033</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4658723</v>
+        <v>4617201</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>21526246</v>
+        <v>21597180</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>201190</v>
+        <v>204889</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>999384</v>
+        <v>959076</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>352009</v>
+        <v>347901</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1750754</v>
+        <v>1750669</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>401806</v>
+        <v>347901</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2002801</v>
+        <v>1750669</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>50125</v>
+        <v>49794</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>250531</v>
+        <v>249602</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>179646</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>897984</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>360692</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1672262</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>120352</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>598614</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>90434</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>449226</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>150879</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>749380</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>518023</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2396230</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>80388</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>400487</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>60178</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>300600</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>100057</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>501219</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>69865</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>350856</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>49795</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>250505</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>39779</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>200248</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>29820</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>150037</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>27561858</v>
+        <v>26448153</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32266817</v>
+        <v>29831005</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>205661</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>955666</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>50043</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>249375</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>79626</v>
+        <v>80258</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>400716</v>
+        <v>399099</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>27482232</v>
+        <v>26573556</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2783440</v>
+        <v>2816591</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>13998375</v>
+        <v>13990319</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24698792</v>
+        <v>23756965</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24698792</v>
+        <v>23756965</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24698792</v>
+        <v>23756965</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24698792</v>
+        <v>23756965</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24698792</v>
+        <v>23756965</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
